--- a/p6_deployment/data/germany/data_preparation/df_tagged.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_tagged.xlsx
@@ -495,24 +495,24 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>h2h_35</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>h2h_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_35</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>h2h_3</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>result</t>
@@ -520,84 +520,84 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_expected_goals_(xg)_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_fouls_against</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_n_player_miss</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_val_player_start</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_sub</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -735,10 +735,10 @@
         <v>132</v>
       </c>
       <c r="G2" t="n">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="H2" t="n">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
         <v>59</v>
@@ -750,10 +750,10 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M2" t="n">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
@@ -806,7 +806,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -829,10 +829,10 @@
         <v>132</v>
       </c>
       <c r="G3" t="n">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="H3" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I3" t="n">
         <v>59</v>
@@ -844,23 +844,15 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M3" t="n">
-        <v>255</v>
-      </c>
-      <c r="N3" t="n">
-        <v>4</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -908,7 +900,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -931,10 +923,10 @@
         <v>132</v>
       </c>
       <c r="G4" t="n">
-        <v>179</v>
+        <v>256</v>
       </c>
       <c r="H4" t="n">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="I4" t="n">
         <v>59</v>
@@ -946,19 +938,23 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M4" t="n">
-        <v>108</v>
+        <v>255</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1</v>
+      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1044,7 +1040,7 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M5" t="n">
         <v>96</v>
@@ -1100,7 +1096,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1117,16 +1113,16 @@
         <v>45522.4375</v>
       </c>
       <c r="E6" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F6" t="n">
         <v>132</v>
       </c>
       <c r="G6" t="n">
-        <v>234</v>
+        <v>129</v>
       </c>
       <c r="H6" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="I6" t="n">
         <v>59</v>
@@ -1138,14 +1134,18 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M6" t="n">
-        <v>2</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>197</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-4</v>
+      </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
+      <c r="P6" t="n">
+        <v>-2</v>
+      </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
@@ -1194,7 +1194,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1211,16 +1211,16 @@
         <v>45522.4375</v>
       </c>
       <c r="E7" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F7" t="n">
         <v>132</v>
       </c>
       <c r="G7" t="n">
-        <v>129</v>
+        <v>234</v>
       </c>
       <c r="H7" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="I7" t="n">
         <v>59</v>
@@ -1232,17 +1232,13 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M7" t="n">
-        <v>197</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-4</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
@@ -1292,7 +1288,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1315,10 +1311,10 @@
         <v>132</v>
       </c>
       <c r="G8" t="n">
-        <v>131</v>
+        <v>263</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
         <v>59</v>
@@ -1330,17 +1326,13 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>160</v>
+        <v>383</v>
       </c>
       <c r="M8" t="n">
-        <v>255</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
@@ -1390,7 +1382,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1413,10 +1405,10 @@
         <v>132</v>
       </c>
       <c r="G9" t="n">
-        <v>263</v>
+        <v>83</v>
       </c>
       <c r="H9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
         <v>59</v>
@@ -1428,15 +1420,23 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>382</v>
+        <v>183</v>
       </c>
       <c r="M9" t="n">
-        <v>108</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+        <v>239</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-7</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-3</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1458,24 +1458,48 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
+      <c r="AK9" t="n">
+        <v>-4.919318181818184</v>
+      </c>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
+      <c r="AM9" t="n">
+        <v>-2.776780303030293</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-2.64014391352778</v>
+      </c>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
+      <c r="AP9" t="n">
+        <v>-474125.2956894047</v>
+      </c>
       <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
+      <c r="AR9" t="n">
+        <v>-1.188431525674087</v>
+      </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>-0.407234848484876</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>-2.177521248774113</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>-0.07386363636363646</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>-0.2099919749555046</v>
+      </c>
       <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
+      <c r="AZ9" t="n">
+        <v>-1478348.484848485</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>2.286628787878787</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>0.2808299432155366</v>
+      </c>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
         <v>0</v>
@@ -1484,7 +1508,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1507,10 +1531,10 @@
         <v>132</v>
       </c>
       <c r="G10" t="n">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
         <v>59</v>
@@ -1522,23 +1546,19 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="M10" t="n">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="N10" t="n">
-        <v>-7</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-7</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -1560,49 +1580,25 @@
       <c r="AH10" t="inlineStr"/>
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="n">
-        <v>-1514375</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>-2.813406553824194</v>
-      </c>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
       <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="n">
-        <v>-2.339856661581507</v>
-      </c>
+      <c r="AN10" t="inlineStr"/>
       <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="n">
-        <v>-0.2391493528507258</v>
-      </c>
+      <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="n">
-        <v>-0.09104585134338095</v>
-      </c>
+      <c r="AR10" t="inlineStr"/>
       <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="n">
-        <v>-2.658333333333331</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>2.583333333333329</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>-5.081818181818178</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>-463268.3951727143</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>-0.5818181818181927</v>
-      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr"/>
-      <c r="BA10" t="n">
-        <v>-1.289992417638295</v>
-      </c>
+      <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="n">
-        <v>-0.05000000000000004</v>
-      </c>
+      <c r="BC10" t="inlineStr"/>
       <c r="BD10" t="n">
         <v>0</v>
       </c>
@@ -1648,7 +1644,7 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M11" t="n">
         <v>16</v>
@@ -1750,10 +1746,10 @@
       <c r="N12" t="n">
         <v>1</v>
       </c>
-      <c r="O12" t="n">
-        <v>1</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
         <v>0</v>
@@ -1849,13 +1845,13 @@
         <v>27</v>
       </c>
       <c r="O13" t="n">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="P13" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1879,48 +1875,48 @@
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="n">
-        <v>24997041.84704185</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>7.894970351996761</v>
-      </c>
-      <c r="AM13" t="inlineStr"/>
+        <v>5.426674148896367</v>
+      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="n">
+        <v>5.554463150018691</v>
+      </c>
       <c r="AN13" t="n">
-        <v>6.985181506726533</v>
+        <v>7.125054868971091</v>
       </c>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="n">
-        <v>0.3418984095614532</v>
+        <v>21872707.76938687</v>
       </c>
       <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="n">
-        <v>-0.7724166390315474</v>
+        <v>-0.7170694187770188</v>
       </c>
       <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="n">
-        <v>5.507359307359295</v>
-      </c>
+      <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="n">
-        <v>1.199999999999999</v>
+        <v>-0.2595585484473872</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.304545454545462</v>
+        <v>6.47627425111358</v>
       </c>
       <c r="AW13" t="n">
-        <v>22738606.18767159</v>
+        <v>0.6347774036662923</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.03838383838387927</v>
+        <v>0.3431987540950161</v>
       </c>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+      <c r="AZ13" t="n">
+        <v>25437945.37972316</v>
+      </c>
       <c r="BA13" t="n">
-        <v>-1.129854557106107</v>
-      </c>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="n">
-        <v>0.6071428571428579</v>
-      </c>
+        <v>1.141578750467648</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>-0.4084854372915743</v>
+      </c>
+      <c r="BC13" t="inlineStr"/>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
@@ -1928,7 +1924,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1945,16 +1941,16 @@
         <v>45521.54166666666</v>
       </c>
       <c r="E14" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F14" t="n">
         <v>132</v>
       </c>
       <c r="G14" t="n">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="H14" t="n">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I14" t="n">
         <v>59</v>
@@ -1966,15 +1962,23 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M14" t="n">
-        <v>96</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-1</v>
+      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2022,7 +2026,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2039,16 +2043,16 @@
         <v>45521.54166666666</v>
       </c>
       <c r="E15" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F15" t="n">
         <v>132</v>
       </c>
       <c r="G15" t="n">
-        <v>180</v>
+        <v>263</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="I15" t="n">
         <v>59</v>
@@ -2060,10 +2064,10 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M15" t="n">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
@@ -2116,7 +2120,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2139,10 +2143,10 @@
         <v>132</v>
       </c>
       <c r="G16" t="n">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="H16" t="n">
-        <v>55</v>
+        <v>4</v>
       </c>
       <c r="I16" t="n">
         <v>59</v>
@@ -2154,23 +2158,15 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M16" t="n">
         <v>49</v>
       </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>3</v>
-      </c>
-      <c r="P16" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-2</v>
-      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -2218,7 +2214,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2235,16 +2231,16 @@
         <v>45521.4375</v>
       </c>
       <c r="E17" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F17" t="n">
         <v>132</v>
       </c>
       <c r="G17" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H17" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>59</v>
@@ -2256,14 +2252,18 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M17" t="n">
-        <v>193</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-1</v>
+      </c>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="P17" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2329,16 +2329,16 @@
         <v>45521.4375</v>
       </c>
       <c r="E18" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F18" t="n">
         <v>132</v>
       </c>
       <c r="G18" t="n">
-        <v>209</v>
+        <v>105</v>
       </c>
       <c r="H18" t="n">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="I18" t="n">
         <v>59</v>
@@ -2350,17 +2350,13 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M18" t="n">
-        <v>179</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-5</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="n">
@@ -2410,7 +2406,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2433,10 +2429,10 @@
         <v>132</v>
       </c>
       <c r="G19" t="n">
-        <v>103</v>
+        <v>209</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="I19" t="n">
         <v>59</v>
@@ -2448,18 +2444,18 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M19" t="n">
-        <v>237</v>
+        <v>179</v>
       </c>
       <c r="N19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
+        <v>-5</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>-2</v>
+      </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="n">
         <v>0</v>
@@ -2508,7 +2504,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2531,10 +2527,10 @@
         <v>132</v>
       </c>
       <c r="G20" t="n">
+        <v>57</v>
+      </c>
+      <c r="H20" t="n">
         <v>30</v>
-      </c>
-      <c r="H20" t="n">
-        <v>59</v>
       </c>
       <c r="I20" t="n">
         <v>59</v>
@@ -2546,23 +2542,15 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>279</v>
+        <v>383</v>
       </c>
       <c r="M20" t="n">
-        <v>193</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-1</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -2584,49 +2572,25 @@
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="n">
-        <v>-7655297.202797204</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>-6.80653556969348</v>
-      </c>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
       <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="n">
-        <v>-6.614782147676891</v>
-      </c>
+      <c r="AN20" t="inlineStr"/>
       <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="n">
-        <v>-0.4481154810102181</v>
-      </c>
+      <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="n">
-        <v>-0.3218382494698631</v>
-      </c>
+      <c r="AR20" t="inlineStr"/>
       <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="n">
-        <v>-8.425174825174793</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>-1.665034965034966</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>-6.361538461538444</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>-4350077.919156868</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>-0.002797202797211185</v>
-      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr"/>
-      <c r="BA20" t="n">
-        <v>1.285272476061948</v>
-      </c>
+      <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="inlineStr"/>
-      <c r="BC20" t="n">
-        <v>-0.7132867132867131</v>
-      </c>
+      <c r="BC20" t="inlineStr"/>
       <c r="BD20" t="n">
         <v>0</v>
       </c>
@@ -2634,7 +2598,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2657,10 +2621,10 @@
         <v>132</v>
       </c>
       <c r="G21" t="n">
-        <v>195</v>
+        <v>30</v>
       </c>
       <c r="H21" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="I21" t="n">
         <v>59</v>
@@ -2672,15 +2636,23 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="M21" t="n">
-        <v>197</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
+        <v>193</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-1</v>
+      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -2702,24 +2674,48 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
+      <c r="AK21" t="n">
+        <v>-6.339090909090913</v>
+      </c>
       <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
+      <c r="AM21" t="n">
+        <v>-8.37833333333333</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>-7.003709852075843</v>
+      </c>
       <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
+      <c r="AP21" t="n">
+        <v>-5100990.884896422</v>
+      </c>
       <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
+      <c r="AR21" t="n">
+        <v>1.214017985785716</v>
+      </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
+      <c r="AU21" t="n">
+        <v>-0.2895454545454186</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>-6.982268056917661</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>-0.7121212121212119</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>-0.4705894794353032</v>
+      </c>
       <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
-      <c r="BA21" t="inlineStr"/>
-      <c r="BB21" t="inlineStr"/>
+      <c r="AZ21" t="n">
+        <v>-7684590.909090909</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>-1.683939393939397</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0.2790326889082451</v>
+      </c>
       <c r="BC21" t="inlineStr"/>
       <c r="BD21" t="n">
         <v>0</v>
@@ -2728,7 +2724,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2751,10 +2747,10 @@
         <v>132</v>
       </c>
       <c r="G22" t="n">
-        <v>57</v>
+        <v>195</v>
       </c>
       <c r="H22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I22" t="n">
         <v>59</v>
@@ -2766,10 +2762,10 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M22" t="n">
-        <v>216</v>
+        <v>197</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -2860,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M23" t="n">
         <v>237</v>
@@ -2954,7 +2950,7 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M24" t="n">
         <v>95</v>
@@ -2962,10 +2958,10 @@
       <c r="N24" t="n">
         <v>-3</v>
       </c>
-      <c r="O24" t="n">
-        <v>-3</v>
-      </c>
-      <c r="P24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>-2</v>
+      </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="n">
         <v>0</v>
@@ -3052,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M25" t="n">
         <v>58</v>
@@ -3060,10 +3056,10 @@
       <c r="N25" t="n">
         <v>-2</v>
       </c>
-      <c r="O25" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
         <v>0</v>
@@ -3150,7 +3146,7 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M26" t="n">
         <v>114</v>
@@ -3252,10 +3248,10 @@
       <c r="N27" t="n">
         <v>-4</v>
       </c>
-      <c r="O27" t="n">
-        <v>-4</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>-2</v>
+      </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>0</v>
@@ -3279,48 +3275,48 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
       <c r="AK27" t="n">
-        <v>-5578679.653679654</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>-7.492063492063494</v>
-      </c>
-      <c r="AM27" t="inlineStr"/>
+        <v>-8.497326203208573</v>
+      </c>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="n">
+        <v>-7.306096256684484</v>
+      </c>
       <c r="AN27" t="n">
-        <v>-6.911706349206355</v>
+        <v>-7.727141801648187</v>
       </c>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="n">
-        <v>-0.4656084656084658</v>
+        <v>-3549902.555514959</v>
       </c>
       <c r="AQ27" t="inlineStr"/>
       <c r="AR27" t="n">
-        <v>-0.8966600529100504</v>
+        <v>-1.46748755734178</v>
       </c>
       <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="n">
-        <v>-7.34415584415585</v>
-      </c>
+      <c r="AT27" t="inlineStr"/>
       <c r="AU27" t="n">
-        <v>0.1504329004329001</v>
+        <v>2.164705882352933</v>
       </c>
       <c r="AV27" t="n">
-        <v>-8.758658008658017</v>
+        <v>-7.42717306052856</v>
       </c>
       <c r="AW27" t="n">
-        <v>-3283664.021164021</v>
+        <v>-0.5927272727272723</v>
       </c>
       <c r="AX27" t="n">
-        <v>2.516233766233768</v>
+        <v>-0.4965362318840578</v>
       </c>
       <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
+      <c r="AZ27" t="n">
+        <v>-5542561.497326203</v>
+      </c>
       <c r="BA27" t="n">
-        <v>-1.249338624338623</v>
-      </c>
-      <c r="BB27" t="inlineStr"/>
-      <c r="BC27" t="n">
-        <v>-0.598484848484848</v>
-      </c>
+        <v>0.04684491978610339</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>-0.7859865627410159</v>
+      </c>
+      <c r="BC27" t="inlineStr"/>
       <c r="BD27" t="n">
         <v>1</v>
       </c>
@@ -3366,7 +3362,7 @@
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M28" t="n">
         <v>58</v>
@@ -3374,10 +3370,10 @@
       <c r="N28" t="n">
         <v>-1</v>
       </c>
-      <c r="O28" t="n">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
         <v>-1</v>
       </c>
-      <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
         <v>0</v>

--- a/p6_deployment/data/germany/data_preparation/df_tagged.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD28"/>
+  <dimension ref="A1:BD32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,84 +520,84 @@
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_last_match_n_matches_last_days</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_n_matches_last_days_against</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_ball_possession</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_ball_possession_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_n_matches_last_days_against</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_points_against</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_shots_on_goal_against</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_goals_against</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_shots_on_goal_against</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
@@ -610,97 +610,97 @@
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_miss</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_pot_player_start</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_miss</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_miss</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_val_player_miss</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_pot_player_sub</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_miss</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_val_player_miss</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
@@ -712,7 +712,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -726,19 +726,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45523.65625</v>
       </c>
       <c r="E2" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F2" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G2" t="n">
-        <v>179</v>
+        <v>113</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I2" t="n">
         <v>59</v>
@@ -750,14 +750,18 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>383</v>
+        <v>17</v>
       </c>
       <c r="M2" t="n">
-        <v>108</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>216</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-4</v>
+      </c>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
+      <c r="P2" t="n">
+        <v>-2</v>
+      </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>0</v>
@@ -781,24 +785,48 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
+      <c r="AL2" t="n">
+        <v>-9.28164983164983</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-13767517.88720539</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-10.04473905723906</v>
+      </c>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>-0.1526691757244976</v>
+      </c>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
+      <c r="AS2" t="n">
+        <v>-0.595412457912458</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.485479797979796</v>
+      </c>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>1.341344011022805</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1.483712121212051</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>-0.4991566855343945</v>
+      </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
+      <c r="BA2" t="n">
+        <v>-5.586116807169432</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>-8.136486850854112</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>-4990525.596615573</v>
+      </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
@@ -806,7 +834,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -820,19 +848,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="E3" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F3" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G3" t="n">
-        <v>225</v>
+        <v>23</v>
       </c>
       <c r="H3" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="I3" t="n">
         <v>59</v>
@@ -844,15 +872,23 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M3" t="n">
-        <v>150</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+        <v>255</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-3</v>
+      </c>
+      <c r="O3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-1</v>
+      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -900,7 +936,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -914,19 +950,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>45522.54166666666</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="E4" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F4" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G4" t="n">
-        <v>256</v>
+        <v>147</v>
       </c>
       <c r="H4" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="I4" t="n">
         <v>59</v>
@@ -938,23 +974,15 @@
         <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M4" t="n">
-        <v>255</v>
-      </c>
-      <c r="N4" t="n">
-        <v>4</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1002,7 +1030,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1016,19 +1044,19 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45523.54166666666</v>
       </c>
       <c r="E5" t="n">
         <v>92</v>
       </c>
       <c r="F5" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G5" t="n">
-        <v>141</v>
+        <v>215</v>
       </c>
       <c r="H5" t="n">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="I5" t="n">
         <v>59</v>
@@ -1040,10 +1068,10 @@
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M5" t="n">
-        <v>96</v>
+        <v>243</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -1096,7 +1124,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1110,19 +1138,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="E6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G6" t="n">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="H6" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I6" t="n">
         <v>59</v>
@@ -1134,18 +1162,14 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M6" t="n">
-        <v>197</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-4</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="n">
-        <v>-2</v>
-      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
@@ -1194,7 +1218,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1208,7 +1232,7 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="E7" t="n">
         <v>93</v>
@@ -1217,10 +1241,10 @@
         <v>132</v>
       </c>
       <c r="G7" t="n">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="H7" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="I7" t="n">
         <v>59</v>
@@ -1232,15 +1256,23 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M7" t="n">
+        <v>255</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" t="n">
         <v>2</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1288,7 +1320,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1302,7 +1334,7 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>45522.4375</v>
+        <v>45522.54166666666</v>
       </c>
       <c r="E8" t="n">
         <v>93</v>
@@ -1311,10 +1343,10 @@
         <v>132</v>
       </c>
       <c r="G8" t="n">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="I8" t="n">
         <v>59</v>
@@ -1326,10 +1358,10 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M8" t="n">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
@@ -1382,7 +1414,7 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1405,10 +1437,10 @@
         <v>132</v>
       </c>
       <c r="G9" t="n">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
         <v>59</v>
@@ -1420,23 +1452,19 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="M9" t="n">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="N9" t="n">
-        <v>-7</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
-        <v>-3</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1458,48 +1486,24 @@
       <c r="AH9" t="inlineStr"/>
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="n">
-        <v>-4.919318181818184</v>
-      </c>
+      <c r="AK9" t="inlineStr"/>
       <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="n">
-        <v>-2.776780303030293</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>-2.64014391352778</v>
-      </c>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
       <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="n">
-        <v>-474125.2956894047</v>
-      </c>
+      <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="n">
-        <v>-1.188431525674087</v>
-      </c>
+      <c r="AR9" t="inlineStr"/>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="n">
-        <v>-0.407234848484876</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>-2.177521248774113</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>-0.07386363636363646</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>-0.2099919749555046</v>
-      </c>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
       <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="n">
-        <v>-1478348.484848485</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>2.286628787878787</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0.2808299432155366</v>
-      </c>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
       <c r="BC9" t="inlineStr"/>
       <c r="BD9" t="n">
         <v>0</v>
@@ -1508,7 +1512,7 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1525,16 +1529,16 @@
         <v>45522.4375</v>
       </c>
       <c r="E10" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F10" t="n">
         <v>132</v>
       </c>
       <c r="G10" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="I10" t="n">
         <v>59</v>
@@ -1546,17 +1550,17 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>160</v>
+        <v>384</v>
       </c>
       <c r="M10" t="n">
-        <v>255</v>
+        <v>197</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="n">
@@ -1606,7 +1610,7 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1620,19 +1624,19 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45522.4375</v>
       </c>
       <c r="E11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G11" t="n">
-        <v>127</v>
+        <v>263</v>
       </c>
       <c r="H11" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
         <v>59</v>
@@ -1644,10 +1648,10 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M11" t="n">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1700,7 +1704,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1714,19 +1718,19 @@
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>45522.33333333334</v>
+        <v>45522.4375</v>
       </c>
       <c r="E12" t="n">
         <v>93</v>
       </c>
       <c r="F12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G12" t="n">
-        <v>162</v>
+        <v>234</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="I12" t="n">
         <v>59</v>
@@ -1738,18 +1742,14 @@
         <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>333</v>
+        <v>384</v>
       </c>
       <c r="M12" t="n">
-        <v>150</v>
-      </c>
-      <c r="N12" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="n">
         <v>0</v>
@@ -1798,7 +1798,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>fcxqFy2l</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1808,50 +1808,50 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>super cup</t>
+          <t>dfb pokal</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45522.4375</v>
       </c>
       <c r="E13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F13" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="H13" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="I13" t="n">
         <v>59</v>
       </c>
       <c r="J13" t="n">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="K13" t="n">
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="M13" t="n">
-        <v>95</v>
+        <v>239</v>
       </c>
       <c r="N13" t="n">
-        <v>27</v>
+        <v>-7</v>
       </c>
       <c r="O13" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="P13" t="n">
-        <v>18</v>
+        <v>-3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1874,49 +1874,49 @@
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="n">
-        <v>5.426674148896367</v>
-      </c>
-      <c r="AL13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="n">
+        <v>-2.758181818181811</v>
+      </c>
       <c r="AM13" t="n">
-        <v>5.554463150018691</v>
+        <v>-1509015.151515151</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.125054868971091</v>
+        <v>-5.030303030303031</v>
       </c>
       <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="n">
-        <v>21872707.76938687</v>
-      </c>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="n">
-        <v>-0.7170694187770188</v>
-      </c>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="n">
-        <v>-0.2595585484473872</v>
-      </c>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="n">
+        <v>0.273591890353913</v>
+      </c>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="n">
+        <v>-0.06666666666666665</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>2.414545454545458</v>
+      </c>
+      <c r="AU13" t="inlineStr"/>
       <c r="AV13" t="n">
-        <v>6.47627425111358</v>
+        <v>-1.17352832564503</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.6347774036662923</v>
+        <v>-0.4084848484848749</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.3431987540950161</v>
+        <v>-0.2144676304287287</v>
       </c>
       <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="n">
-        <v>25437945.37972316</v>
-      </c>
+      <c r="AZ13" t="inlineStr"/>
       <c r="BA13" t="n">
-        <v>1.141578750467648</v>
+        <v>-2.234716017095892</v>
       </c>
       <c r="BB13" t="n">
-        <v>-0.4084854372915743</v>
-      </c>
-      <c r="BC13" t="inlineStr"/>
+        <v>-2.738820481154576</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>-459870.6685191237</v>
+      </c>
       <c r="BD13" t="n">
         <v>0</v>
       </c>
@@ -1924,7 +1924,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1938,19 +1938,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.4375</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F14" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G14" t="n">
-        <v>218</v>
+        <v>141</v>
       </c>
       <c r="H14" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="I14" t="n">
         <v>59</v>
@@ -1962,23 +1962,15 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M14" t="n">
-        <v>49</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-1</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2026,7 +2018,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2040,19 +2032,19 @@
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="E15" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F15" t="n">
         <v>132</v>
       </c>
       <c r="G15" t="n">
-        <v>263</v>
+        <v>162</v>
       </c>
       <c r="H15" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
         <v>59</v>
@@ -2064,14 +2056,18 @@
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>383</v>
+        <v>333</v>
       </c>
       <c r="M15" t="n">
-        <v>96</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
+        <v>150</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
+      </c>
       <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="n">
         <v>0</v>
@@ -2120,7 +2116,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2134,19 +2130,19 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>45521.54166666666</v>
+        <v>45522.33333333334</v>
       </c>
       <c r="E16" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F16" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G16" t="n">
-        <v>180</v>
+        <v>127</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="I16" t="n">
         <v>59</v>
@@ -2158,10 +2154,10 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M16" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
@@ -2214,7 +2210,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>fcxqFy2l</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2224,47 +2220,51 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>dfb pokal</t>
+          <t>super cup</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="E17" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F17" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G17" t="n">
-        <v>103</v>
+        <v>13</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="I17" t="n">
         <v>59</v>
       </c>
       <c r="J17" t="n">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="K17" t="n">
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>383</v>
+        <v>17</v>
       </c>
       <c r="M17" t="n">
-        <v>237</v>
+        <v>95</v>
       </c>
       <c r="N17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O17" t="inlineStr"/>
+        <v>27</v>
+      </c>
+      <c r="O17" t="n">
+        <v>4</v>
+      </c>
       <c r="P17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3</v>
+      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -2287,24 +2287,48 @@
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
+      <c r="AL17" t="n">
+        <v>5.554463150018691</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>25437945.37972316</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>5.426674148896367</v>
+      </c>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
+      <c r="AQ17" t="n">
+        <v>-0.4084854372915743</v>
+      </c>
       <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
+      <c r="AS17" t="n">
+        <v>0.6347774036662923</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1.141578750467648</v>
+      </c>
       <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>-0.7170694187770188</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>-0.2595585484473872</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0.3431987540950161</v>
+      </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
+      <c r="BA17" t="n">
+        <v>6.47627425111358</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>7.125054868971091</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>21872707.76938687</v>
+      </c>
       <c r="BD17" t="n">
         <v>0</v>
       </c>
@@ -2312,7 +2336,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2326,7 +2350,7 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="E18" t="n">
         <v>92</v>
@@ -2335,10 +2359,10 @@
         <v>132</v>
       </c>
       <c r="G18" t="n">
-        <v>105</v>
+        <v>263</v>
       </c>
       <c r="H18" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="I18" t="n">
         <v>59</v>
@@ -2350,10 +2374,10 @@
         <v>1</v>
       </c>
       <c r="L18" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M18" t="n">
-        <v>193</v>
+        <v>96</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -2406,7 +2430,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2420,7 +2444,7 @@
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="E19" t="n">
         <v>93</v>
@@ -2429,10 +2453,10 @@
         <v>132</v>
       </c>
       <c r="G19" t="n">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="H19" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="I19" t="n">
         <v>59</v>
@@ -2444,19 +2468,23 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M19" t="n">
-        <v>179</v>
+        <v>49</v>
       </c>
       <c r="N19" t="n">
-        <v>-5</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-2</v>
+      </c>
       <c r="P19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1</v>
+      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -2504,7 +2532,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2518,19 +2546,19 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>45521.4375</v>
+        <v>45521.54166666666</v>
       </c>
       <c r="E20" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F20" t="n">
         <v>132</v>
       </c>
       <c r="G20" t="n">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="H20" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I20" t="n">
         <v>59</v>
@@ -2542,10 +2570,10 @@
         <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M20" t="n">
-        <v>216</v>
+        <v>49</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -2598,7 +2626,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2618,13 +2646,13 @@
         <v>92</v>
       </c>
       <c r="F21" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G21" t="n">
-        <v>30</v>
+        <v>195</v>
       </c>
       <c r="H21" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="I21" t="n">
         <v>59</v>
@@ -2636,23 +2664,15 @@
         <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>279</v>
+        <v>384</v>
       </c>
       <c r="M21" t="n">
-        <v>193</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-1</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -2674,48 +2694,24 @@
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="n">
-        <v>-6.339090909090913</v>
-      </c>
+      <c r="AK21" t="inlineStr"/>
       <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="n">
-        <v>-8.37833333333333</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>-7.003709852075843</v>
-      </c>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
       <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="n">
-        <v>-5100990.884896422</v>
-      </c>
+      <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="n">
-        <v>1.214017985785716</v>
-      </c>
+      <c r="AR21" t="inlineStr"/>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="n">
-        <v>-0.2895454545454186</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>-6.982268056917661</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>-0.7121212121212119</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>-0.4705894794353032</v>
-      </c>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
       <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="n">
-        <v>-7684590.909090909</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>-1.683939393939397</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0.2790326889082451</v>
-      </c>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
       <c r="BC21" t="inlineStr"/>
       <c r="BD21" t="n">
         <v>0</v>
@@ -2724,7 +2720,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2744,13 +2740,13 @@
         <v>92</v>
       </c>
       <c r="F22" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G22" t="n">
-        <v>195</v>
+        <v>30</v>
       </c>
       <c r="H22" t="n">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="I22" t="n">
         <v>59</v>
@@ -2762,15 +2758,23 @@
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>383</v>
+        <v>279</v>
       </c>
       <c r="M22" t="n">
-        <v>197</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
+        <v>193</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-1</v>
+      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -2793,24 +2797,48 @@
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
+      <c r="AL22" t="n">
+        <v>-8.37833333333333</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>-7684590.909090909</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>-6.339090909090913</v>
+      </c>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
+      <c r="AQ22" t="n">
+        <v>0.2790326889082451</v>
+      </c>
       <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
+      <c r="AS22" t="n">
+        <v>-0.7121212121212119</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>-1.683939393939397</v>
+      </c>
       <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
+      <c r="AV22" t="n">
+        <v>1.214017985785716</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>-0.2895454545454186</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>-0.4705894794353034</v>
+      </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="inlineStr"/>
-      <c r="BB22" t="inlineStr"/>
-      <c r="BC22" t="inlineStr"/>
+      <c r="BA22" t="n">
+        <v>-6.982268056917661</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>-7.003709852075843</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>-5100990.884896422</v>
+      </c>
       <c r="BD22" t="n">
         <v>0</v>
       </c>
@@ -2818,7 +2846,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2832,19 +2860,19 @@
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45521.4375</v>
       </c>
       <c r="E23" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F23" t="n">
         <v>132</v>
       </c>
       <c r="G23" t="n">
-        <v>144</v>
+        <v>57</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="I23" t="n">
         <v>59</v>
@@ -2856,10 +2884,10 @@
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M23" t="n">
-        <v>237</v>
+        <v>216</v>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
@@ -2912,7 +2940,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2926,19 +2954,19 @@
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>45521.33333333334</v>
+        <v>45521.4375</v>
       </c>
       <c r="E24" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F24" t="n">
         <v>132</v>
       </c>
       <c r="G24" t="n">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="H24" t="n">
-        <v>9</v>
+        <v>70</v>
       </c>
       <c r="I24" t="n">
         <v>59</v>
@@ -2950,13 +2978,13 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M24" t="n">
-        <v>95</v>
+        <v>179</v>
       </c>
       <c r="N24" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
@@ -3010,7 +3038,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3024,19 +3052,19 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>45520.65625</v>
+        <v>45521.4375</v>
       </c>
       <c r="E25" t="n">
         <v>92</v>
       </c>
       <c r="F25" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G25" t="n">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="H25" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I25" t="n">
         <v>59</v>
@@ -3048,18 +3076,14 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M25" t="n">
-        <v>58</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-2</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="n">
-        <v>-1</v>
-      </c>
+      <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="n">
         <v>0</v>
@@ -3108,7 +3132,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3122,7 +3146,7 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.4375</v>
       </c>
       <c r="E26" t="n">
         <v>93</v>
@@ -3131,10 +3155,10 @@
         <v>132</v>
       </c>
       <c r="G26" t="n">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="H26" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>59</v>
@@ -3146,14 +3170,18 @@
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M26" t="n">
-        <v>114</v>
-      </c>
-      <c r="N26" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1</v>
+      </c>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="n">
         <v>0</v>
@@ -3202,7 +3230,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3216,19 +3244,19 @@
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="E27" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F27" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G27" t="n">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="H27" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I27" t="n">
         <v>59</v>
@@ -3240,18 +3268,14 @@
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>160</v>
+        <v>384</v>
       </c>
       <c r="M27" t="n">
-        <v>243</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-4</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
-        <v>-2</v>
-      </c>
+      <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="n">
         <v>0</v>
@@ -3274,57 +3298,33 @@
       <c r="AH27" t="inlineStr"/>
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="n">
-        <v>-8.497326203208573</v>
-      </c>
+      <c r="AK27" t="inlineStr"/>
       <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="n">
-        <v>-7.306096256684484</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>-7.727141801648187</v>
-      </c>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
       <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="n">
-        <v>-3549902.555514959</v>
-      </c>
+      <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="n">
-        <v>-1.46748755734178</v>
-      </c>
+      <c r="AR27" t="inlineStr"/>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="n">
-        <v>2.164705882352933</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>-7.42717306052856</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>-0.5927272727272723</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>-0.4965362318840578</v>
-      </c>
+      <c r="AU27" t="inlineStr"/>
+      <c r="AV27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr"/>
+      <c r="AX27" t="inlineStr"/>
       <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="n">
-        <v>-5542561.497326203</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0.04684491978610339</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>-0.7859865627410159</v>
-      </c>
+      <c r="AZ27" t="inlineStr"/>
+      <c r="BA27" t="inlineStr"/>
+      <c r="BB27" t="inlineStr"/>
       <c r="BC27" t="inlineStr"/>
       <c r="BD27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3338,7 +3338,7 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>45520.54166666666</v>
+        <v>45521.33333333334</v>
       </c>
       <c r="E28" t="n">
         <v>92</v>
@@ -3347,10 +3347,10 @@
         <v>132</v>
       </c>
       <c r="G28" t="n">
-        <v>204</v>
+        <v>247</v>
       </c>
       <c r="H28" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="I28" t="n">
         <v>59</v>
@@ -3362,17 +3362,17 @@
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M28" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="N28" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="n">
@@ -3419,6 +3419,418 @@
         <v>0</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>45520.65625</v>
+      </c>
+      <c r="E29" t="n">
+        <v>92</v>
+      </c>
+      <c r="F29" t="n">
+        <v>133</v>
+      </c>
+      <c r="G29" t="n">
+        <v>235</v>
+      </c>
+      <c r="H29" t="n">
+        <v>69</v>
+      </c>
+      <c r="I29" t="n">
+        <v>59</v>
+      </c>
+      <c r="J29" t="n">
+        <v>593</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>384</v>
+      </c>
+      <c r="M29" t="n">
+        <v>58</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-2</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+      <c r="AH29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AU29" t="inlineStr"/>
+      <c r="AV29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr"/>
+      <c r="AX29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr"/>
+      <c r="BB29" t="inlineStr"/>
+      <c r="BC29" t="inlineStr"/>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="E30" t="n">
+        <v>93</v>
+      </c>
+      <c r="F30" t="n">
+        <v>132</v>
+      </c>
+      <c r="G30" t="n">
+        <v>153</v>
+      </c>
+      <c r="H30" t="n">
+        <v>24</v>
+      </c>
+      <c r="I30" t="n">
+        <v>59</v>
+      </c>
+      <c r="J30" t="n">
+        <v>593</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" t="n">
+        <v>384</v>
+      </c>
+      <c r="M30" t="n">
+        <v>114</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AU30" t="inlineStr"/>
+      <c r="AV30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr"/>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
+      <c r="BA30" t="inlineStr"/>
+      <c r="BB30" t="inlineStr"/>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="E31" t="n">
+        <v>92</v>
+      </c>
+      <c r="F31" t="n">
+        <v>132</v>
+      </c>
+      <c r="G31" t="n">
+        <v>102</v>
+      </c>
+      <c r="H31" t="n">
+        <v>22</v>
+      </c>
+      <c r="I31" t="n">
+        <v>59</v>
+      </c>
+      <c r="J31" t="n">
+        <v>593</v>
+      </c>
+      <c r="K31" t="n">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>160</v>
+      </c>
+      <c r="M31" t="n">
+        <v>243</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-4</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="n">
+        <v>-7.315454545454543</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>-5551460.227272727</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>-8.568181818181827</v>
+      </c>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="n">
+        <v>-0.7650000431331989</v>
+      </c>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="n">
+        <v>-0.5927272727272723</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0.09363636363636729</v>
+      </c>
+      <c r="AU31" t="inlineStr"/>
+      <c r="AV31" t="n">
+        <v>-1.476321299171843</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>2.212499999999977</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>-0.4965362318840578</v>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr"/>
+      <c r="BA31" t="n">
+        <v>-7.385863828502423</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>-7.660454710144919</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>-3540577.341054174</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>dfb pokal</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="E32" t="n">
+        <v>92</v>
+      </c>
+      <c r="F32" t="n">
+        <v>132</v>
+      </c>
+      <c r="G32" t="n">
+        <v>204</v>
+      </c>
+      <c r="H32" t="n">
+        <v>60</v>
+      </c>
+      <c r="I32" t="n">
+        <v>59</v>
+      </c>
+      <c r="J32" t="n">
+        <v>593</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>384</v>
+      </c>
+      <c r="M32" t="n">
+        <v>58</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr"/>
+      <c r="AB32" t="inlineStr"/>
+      <c r="AC32" t="inlineStr"/>
+      <c r="AD32" t="inlineStr"/>
+      <c r="AE32" t="inlineStr"/>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="inlineStr"/>
+      <c r="AH32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr"/>
+      <c r="AJ32" t="inlineStr"/>
+      <c r="AK32" t="inlineStr"/>
+      <c r="AL32" t="inlineStr"/>
+      <c r="AM32" t="inlineStr"/>
+      <c r="AN32" t="inlineStr"/>
+      <c r="AO32" t="inlineStr"/>
+      <c r="AP32" t="inlineStr"/>
+      <c r="AQ32" t="inlineStr"/>
+      <c r="AR32" t="inlineStr"/>
+      <c r="AS32" t="inlineStr"/>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AU32" t="inlineStr"/>
+      <c r="AV32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr"/>
+      <c r="AX32" t="inlineStr"/>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr"/>
+      <c r="BA32" t="inlineStr"/>
+      <c r="BB32" t="inlineStr"/>
+      <c r="BC32" t="inlineStr"/>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/germany/data_preparation/df_tagged.xlsx
+++ b/p6_deployment/data/germany/data_preparation/df_tagged.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD32"/>
+  <dimension ref="A1:BB32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,252 +460,242 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>id_team_home</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>id_team_away</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>id_coach_home</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_coach_away</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>h2h_35</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>h2h_3</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>h2h_35_segun_loc</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>h2h_3_segun_loc</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>result</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
+          <t>dif_mean_hei_player_start</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_start</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_start</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_start</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_sub</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_start</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_hei_player_sub</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_int_rep_player_start</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_pot_player_sub</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_val_player_sub</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_rat_player_sub</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_age_player_sub</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>is_rival_match</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goals_against</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_points_against</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_ball_possession_against</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_fouls_against</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dif_mean_last_match_goal_attempts_against</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>dif_mean_last_match_n_matches_last_days</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_n_matches_last_days_against</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goal_attempts_against</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_expected_goals_(xg)_against</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_ball_possession_against</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_fouls_against</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_points_against</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_last_match_shots_on_goal_against</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_last_match_goals_against</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_home_against</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>mean_last_match_mean_rat_player_start_away_against</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_rat_player_miss</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_hei_player_miss</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_start</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_start</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_start</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_rat_player_miss</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>dif_sum_pot_player_miss</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_age_player_miss</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_sub</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>dif_mean_int_rep_player_miss</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_start</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_start</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>dif_sum_pot_player_miss</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_age_player_sub</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_hei_player_start</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_int_rep_player_sub</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>dif_sum_val_player_miss</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>dif_n_player_miss</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_rat_player_sub</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_pot_player_sub</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>dif_mean_val_player_sub</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>is_rival_match</t>
         </is>
       </c>
     </row>
@@ -735,106 +725,104 @@
         <v>133</v>
       </c>
       <c r="G2" t="n">
+        <v>23325</v>
+      </c>
+      <c r="H2" t="n">
         <v>113</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>12</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>59</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>593</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>17</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>216</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>-4</v>
       </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="n">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
         <v>-2</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="n">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>1.386219336219341</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.307371332371336</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-9.377958152958144</v>
+      </c>
+      <c r="V2" t="n">
+        <v>-13994968.13371813</v>
+      </c>
+      <c r="W2" t="n">
+        <v>-0.4036070289359763</v>
+      </c>
+      <c r="X2" t="n">
+        <v>-10.07853535353534</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>-1.594049517733708</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>-0.5896945646945648</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>-8.366329175210737</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>-4193764.608016253</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>-4.856144148249413</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>2.042059220019745</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0</v>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="n">
-        <v>-9.28164983164983</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-13767517.88720539</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-10.04473905723906</v>
-      </c>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="n">
-        <v>-0.1526691757244976</v>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="n">
-        <v>-0.595412457912458</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1.485479797979796</v>
-      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="n">
-        <v>1.341344011022805</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>1.483712121212051</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>-0.4991566855343945</v>
-      </c>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="n">
-        <v>-5.586116807169432</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>-8.136486850854112</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>-4990525.596615573</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -851,47 +839,39 @@
         <v>45523.54166666666</v>
       </c>
       <c r="E3" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F3" t="n">
         <v>133</v>
       </c>
       <c r="G3" t="n">
-        <v>23</v>
+        <v>20500</v>
       </c>
       <c r="H3" t="n">
-        <v>25</v>
+        <v>147</v>
       </c>
       <c r="I3" t="n">
+        <v>48</v>
+      </c>
+      <c r="J3" t="n">
         <v>59</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>593</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="n">
-        <v>384</v>
-      </c>
       <c r="M3" t="n">
-        <v>255</v>
+        <v>385</v>
       </c>
       <c r="N3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -904,7 +884,9 @@
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
@@ -928,15 +910,11 @@
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -953,39 +931,39 @@
         <v>45523.54166666666</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
         <v>133</v>
       </c>
       <c r="G4" t="n">
-        <v>147</v>
+        <v>9500</v>
       </c>
       <c r="H4" t="n">
-        <v>48</v>
+        <v>215</v>
       </c>
       <c r="I4" t="n">
+        <v>73</v>
+      </c>
+      <c r="J4" t="n">
         <v>59</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>593</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="n">
-        <v>384</v>
-      </c>
       <c r="M4" t="n">
-        <v>87</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>385</v>
+      </c>
+      <c r="N4" t="n">
+        <v>243</v>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -998,7 +976,9 @@
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
@@ -1022,15 +1002,11 @@
       <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1053,32 +1029,40 @@
         <v>133</v>
       </c>
       <c r="G5" t="n">
-        <v>215</v>
+        <v>22450</v>
       </c>
       <c r="H5" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="I5" t="n">
+        <v>25</v>
+      </c>
+      <c r="J5" t="n">
         <v>59</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>593</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="n">
-        <v>384</v>
-      </c>
       <c r="M5" t="n">
-        <v>243</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>385</v>
+      </c>
+      <c r="N5" t="n">
+        <v>255</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
@@ -1092,7 +1076,9 @@
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
@@ -1116,15 +1102,11 @@
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1144,35 +1126,43 @@
         <v>93</v>
       </c>
       <c r="F6" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G6" t="n">
-        <v>179</v>
+        <v>32249</v>
       </c>
       <c r="H6" t="n">
-        <v>20</v>
+        <v>256</v>
       </c>
       <c r="I6" t="n">
+        <v>71</v>
+      </c>
+      <c r="J6" t="n">
         <v>59</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>593</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="n">
-        <v>384</v>
-      </c>
       <c r="M6" t="n">
-        <v>108</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+        <v>385</v>
+      </c>
+      <c r="N6" t="n">
+        <v>255</v>
+      </c>
+      <c r="O6" t="n">
+        <v>4</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2</v>
+      </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
@@ -1186,7 +1176,9 @@
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
@@ -1210,15 +1202,11 @@
       <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1241,41 +1229,33 @@
         <v>132</v>
       </c>
       <c r="G7" t="n">
-        <v>256</v>
+        <v>13696</v>
       </c>
       <c r="H7" t="n">
-        <v>71</v>
+        <v>225</v>
       </c>
       <c r="I7" t="n">
+        <v>83</v>
+      </c>
+      <c r="J7" t="n">
         <v>59</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>593</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>384</v>
-      </c>
       <c r="M7" t="n">
-        <v>255</v>
+        <v>385</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -1288,7 +1268,9 @@
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
@@ -1312,15 +1294,11 @@
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1340,36 +1318,36 @@
         <v>93</v>
       </c>
       <c r="F8" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G8" t="n">
-        <v>225</v>
+        <v>10059</v>
       </c>
       <c r="H8" t="n">
-        <v>83</v>
+        <v>179</v>
       </c>
       <c r="I8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" t="n">
         <v>59</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>593</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="n">
-        <v>384</v>
-      </c>
       <c r="M8" t="n">
-        <v>150</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>385</v>
+      </c>
+      <c r="N8" t="n">
+        <v>108</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1382,7 +1360,9 @@
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
@@ -1406,15 +1386,11 @@
       <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1434,40 +1410,36 @@
         <v>93</v>
       </c>
       <c r="F9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G9" t="n">
-        <v>131</v>
+        <v>10000</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>263</v>
       </c>
       <c r="I9" t="n">
+        <v>8</v>
+      </c>
+      <c r="J9" t="n">
         <v>59</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>593</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="n">
-        <v>160</v>
-      </c>
       <c r="M9" t="n">
-        <v>255</v>
+        <v>385</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -1480,7 +1452,9 @@
       <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
@@ -1504,15 +1478,11 @@
       <c r="AZ9" t="inlineStr"/>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1529,43 +1499,37 @@
         <v>45522.4375</v>
       </c>
       <c r="E10" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F10" t="n">
-        <v>132</v>
-      </c>
-      <c r="G10" t="n">
-        <v>129</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>45</v>
+        <v>234</v>
       </c>
       <c r="I10" t="n">
+        <v>23</v>
+      </c>
+      <c r="J10" t="n">
         <v>59</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>593</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="n">
-        <v>384</v>
-      </c>
       <c r="M10" t="n">
-        <v>197</v>
+        <v>385</v>
       </c>
       <c r="N10" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="n">
-        <v>-2</v>
-      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -1578,7 +1542,9 @@
       <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
@@ -1602,15 +1568,11 @@
       <c r="AZ10" t="inlineStr"/>
       <c r="BA10" t="inlineStr"/>
       <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1630,49 +1592,83 @@
         <v>93</v>
       </c>
       <c r="F11" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G11" t="n">
-        <v>263</v>
+        <v>29000</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="I11" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" t="n">
         <v>59</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>593</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="n">
-        <v>384</v>
-      </c>
       <c r="M11" t="n">
-        <v>108</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
+        <v>183</v>
+      </c>
+      <c r="N11" t="n">
+        <v>239</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-7</v>
+      </c>
+      <c r="P11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-3</v>
+      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>-0.9051948051948671</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.415584415584412</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-2.728571428571428</v>
+      </c>
+      <c r="V11" t="n">
+        <v>-1520649.350649351</v>
+      </c>
+      <c r="W11" t="n">
+        <v>-0.230265103753172</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-4.963636363636382</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4995336425950256</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>-0.07142857142857162</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>-3.333470192043251</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>-511996.1037427941</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>-2.054266748652182</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>-0.5918010606225685</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
@@ -1696,15 +1692,11 @@
       <c r="AZ11" t="inlineStr"/>
       <c r="BA11" t="inlineStr"/>
       <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1721,39 +1713,37 @@
         <v>45522.4375</v>
       </c>
       <c r="E12" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F12" t="n">
-        <v>133</v>
-      </c>
-      <c r="G12" t="n">
-        <v>234</v>
-      </c>
+        <v>134</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="I12" t="n">
+        <v>38</v>
+      </c>
+      <c r="J12" t="n">
         <v>59</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>593</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="n">
-        <v>384</v>
-      </c>
       <c r="M12" t="n">
-        <v>2</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>385</v>
+      </c>
+      <c r="N12" t="n">
+        <v>96</v>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -1766,7 +1756,9 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
       <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
@@ -1790,15 +1782,11 @@
       <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1821,41 +1809,37 @@
         <v>132</v>
       </c>
       <c r="G13" t="n">
-        <v>83</v>
+        <v>15210</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>131</v>
       </c>
       <c r="I13" t="n">
+        <v>11</v>
+      </c>
+      <c r="J13" t="n">
         <v>59</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>593</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="n">
-        <v>183</v>
-      </c>
       <c r="M13" t="n">
-        <v>239</v>
+        <v>160</v>
       </c>
       <c r="N13" t="n">
-        <v>-7</v>
+        <v>255</v>
       </c>
       <c r="O13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P13" t="n">
-        <v>-3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="P13" t="inlineStr"/>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -1868,63 +1852,37 @@
       <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
       <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="n">
-        <v>-2.758181818181811</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>-1509015.151515151</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>-5.030303030303031</v>
-      </c>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="n">
-        <v>0.273591890353913</v>
-      </c>
+      <c r="AQ13" t="inlineStr"/>
       <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="n">
-        <v>-0.06666666666666665</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>2.414545454545458</v>
-      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
       <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="n">
-        <v>-1.17352832564503</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-0.4084848484848749</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>-0.2144676304287287</v>
-      </c>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr"/>
-      <c r="BA13" t="n">
-        <v>-2.234716017095892</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>-2.738820481154576</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>-459870.6685191237</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1944,36 +1902,40 @@
         <v>92</v>
       </c>
       <c r="F14" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="G14" t="n">
-        <v>141</v>
+        <v>15414</v>
       </c>
       <c r="H14" t="n">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="I14" t="n">
+        <v>45</v>
+      </c>
+      <c r="J14" t="n">
         <v>59</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>593</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="n">
-        <v>384</v>
-      </c>
       <c r="M14" t="n">
-        <v>96</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+        <v>385</v>
+      </c>
+      <c r="N14" t="n">
+        <v>197</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-4</v>
+      </c>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
+      <c r="Q14" t="n">
+        <v>-2</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -1986,7 +1948,9 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
@@ -2010,10 +1974,6 @@
       <c r="AZ14" t="inlineStr"/>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -2041,37 +2001,37 @@
         <v>132</v>
       </c>
       <c r="G15" t="n">
+        <v>16003</v>
+      </c>
+      <c r="H15" t="n">
         <v>162</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>5</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>59</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>593</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="n">
-        <v>333</v>
-      </c>
       <c r="M15" t="n">
+        <v>385</v>
+      </c>
+      <c r="N15" t="n">
         <v>150</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>1</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="n">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
+      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -2084,7 +2044,9 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
@@ -2108,10 +2070,6 @@
       <c r="AZ15" t="inlineStr"/>
       <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -2136,36 +2094,34 @@
         <v>92</v>
       </c>
       <c r="F16" t="n">
-        <v>133</v>
-      </c>
-      <c r="G16" t="n">
+        <v>134</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
         <v>127</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>58</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>59</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>593</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="n">
-        <v>384</v>
-      </c>
       <c r="M16" t="n">
+        <v>385</v>
+      </c>
+      <c r="N16" t="n">
         <v>16</v>
       </c>
-      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -2178,7 +2134,9 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
       <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
@@ -2202,10 +2160,6 @@
       <c r="AZ16" t="inlineStr"/>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -2233,110 +2187,108 @@
         <v>131</v>
       </c>
       <c r="G17" t="n">
+        <v>30210</v>
+      </c>
+      <c r="H17" t="n">
         <v>13</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>66</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>59</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>594</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>17</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>95</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>27</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>4</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>18</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>3</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
+        <v>0.5957653457653578</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.253729603729603</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.122144522144509</v>
+      </c>
+      <c r="V17" t="n">
+        <v>20477311.57731158</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.4897894275611663</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.910023310023305</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-0.9577051169442825</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.5293706293706295</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>8.819984906397934</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>30268860.95310687</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.873451518288476</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>-1.420749500097319</v>
+      </c>
+      <c r="AE17" t="n">
         <v>0</v>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
-      <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="n">
-        <v>5.554463150018691</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>25437945.37972316</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>5.426674148896367</v>
-      </c>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="n">
-        <v>-0.4084854372915743</v>
-      </c>
+      <c r="AQ17" t="inlineStr"/>
       <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="n">
-        <v>0.6347774036662923</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>1.141578750467648</v>
-      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
       <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="n">
-        <v>-0.7170694187770188</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>-0.2595585484473872</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0.3431987540950161</v>
-      </c>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr"/>
-      <c r="BA17" t="n">
-        <v>6.47627425111358</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>7.125054868971091</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>21872707.76938687</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2353,38 +2305,46 @@
         <v>45521.54166666666</v>
       </c>
       <c r="E18" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F18" t="n">
         <v>132</v>
       </c>
       <c r="G18" t="n">
-        <v>263</v>
+        <v>27332</v>
       </c>
       <c r="H18" t="n">
-        <v>67</v>
+        <v>218</v>
       </c>
       <c r="I18" t="n">
+        <v>55</v>
+      </c>
+      <c r="J18" t="n">
         <v>59</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>593</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="n">
-        <v>384</v>
-      </c>
       <c r="M18" t="n">
-        <v>96</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
+        <v>385</v>
+      </c>
+      <c r="N18" t="n">
+        <v>49</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1</v>
+      </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -2398,7 +2358,9 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
@@ -2422,15 +2384,11 @@
       <c r="AZ18" t="inlineStr"/>
       <c r="BA18" t="inlineStr"/>
       <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2453,41 +2411,33 @@
         <v>132</v>
       </c>
       <c r="G19" t="n">
-        <v>218</v>
+        <v>31026</v>
       </c>
       <c r="H19" t="n">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="n">
         <v>59</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>593</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="n">
-        <v>384</v>
-      </c>
       <c r="M19" t="n">
+        <v>385</v>
+      </c>
+      <c r="N19" t="n">
         <v>49</v>
       </c>
-      <c r="N19" t="n">
-        <v>3</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-2</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -2500,7 +2450,9 @@
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
@@ -2524,15 +2476,11 @@
       <c r="AZ19" t="inlineStr"/>
       <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2549,39 +2497,39 @@
         <v>45521.54166666666</v>
       </c>
       <c r="E20" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F20" t="n">
         <v>132</v>
       </c>
       <c r="G20" t="n">
-        <v>180</v>
+        <v>17849</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>263</v>
       </c>
       <c r="I20" t="n">
+        <v>67</v>
+      </c>
+      <c r="J20" t="n">
         <v>59</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>593</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="n">
-        <v>384</v>
-      </c>
       <c r="M20" t="n">
-        <v>49</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
+        <v>385</v>
+      </c>
+      <c r="N20" t="n">
+        <v>96</v>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
+      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -2594,7 +2542,9 @@
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
@@ -2618,10 +2568,6 @@
       <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="inlineStr"/>
-      <c r="BC20" t="inlineStr"/>
-      <c r="BD20" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2649,33 +2595,33 @@
         <v>133</v>
       </c>
       <c r="G21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="H21" t="n">
         <v>195</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>29</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>59</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>593</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="n">
-        <v>384</v>
-      </c>
       <c r="M21" t="n">
+        <v>385</v>
+      </c>
+      <c r="N21" t="n">
         <v>197</v>
       </c>
-      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -2688,7 +2634,9 @@
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
@@ -2712,10 +2660,6 @@
       <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="inlineStr"/>
       <c r="BB21" t="inlineStr"/>
-      <c r="BC21" t="inlineStr"/>
-      <c r="BD21" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2743,105 +2687,103 @@
         <v>133</v>
       </c>
       <c r="G22" t="n">
+        <v>16667</v>
+      </c>
+      <c r="H22" t="n">
         <v>30</v>
-      </c>
-      <c r="H22" t="n">
-        <v>59</v>
       </c>
       <c r="I22" t="n">
         <v>59</v>
       </c>
       <c r="J22" t="n">
+        <v>59</v>
+      </c>
+      <c r="K22" t="n">
         <v>593</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>279</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>193</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>-1</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>1</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>-1</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
+        <v>0.012337662337643</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-1.63463203463203</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-8.457575757575754</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-7344080.086580085</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-0.4320534125167992</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-6.20930735930736</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>-0.5932105431798789</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>-0.6969696969696966</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>-6.910317638687815</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>-4508584.188538115</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>-6.568198738305384</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.9483970991142385</v>
+      </c>
+      <c r="AE22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
-      <c r="Y22" t="inlineStr"/>
-      <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="n">
-        <v>-8.37833333333333</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>-7684590.909090909</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>-6.339090909090913</v>
-      </c>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="n">
-        <v>0.2790326889082451</v>
-      </c>
+      <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="n">
-        <v>-0.7121212121212119</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>-1.683939393939397</v>
-      </c>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
       <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="n">
-        <v>1.214017985785716</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>-0.2895454545454186</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>-0.4705894794353034</v>
-      </c>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
-      <c r="BA22" t="n">
-        <v>-6.982268056917661</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>-7.003709852075843</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>-5100990.884896422</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>0</v>
-      </c>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2869,33 +2811,33 @@
         <v>132</v>
       </c>
       <c r="G23" t="n">
+        <v>20352</v>
+      </c>
+      <c r="H23" t="n">
         <v>57</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>30</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>59</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>593</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="n">
-        <v>384</v>
-      </c>
       <c r="M23" t="n">
+        <v>385</v>
+      </c>
+      <c r="N23" t="n">
         <v>216</v>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
+      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -2908,7 +2850,9 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
@@ -2932,10 +2876,6 @@
       <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="inlineStr"/>
-      <c r="BC23" t="inlineStr"/>
-      <c r="BD23" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2963,37 +2903,37 @@
         <v>132</v>
       </c>
       <c r="G24" t="n">
+        <v>15800</v>
+      </c>
+      <c r="H24" t="n">
         <v>209</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>70</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>59</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>593</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="n">
-        <v>384</v>
-      </c>
       <c r="M24" t="n">
+        <v>385</v>
+      </c>
+      <c r="N24" t="n">
         <v>179</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>-5</v>
       </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="n">
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="n">
         <v>-2</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
+      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
@@ -3006,7 +2946,9 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
       <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
@@ -3030,10 +2972,6 @@
       <c r="AZ24" t="inlineStr"/>
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr"/>
-      <c r="BC24" t="inlineStr"/>
-      <c r="BD24" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -3061,33 +2999,33 @@
         <v>133</v>
       </c>
       <c r="G25" t="n">
+        <v>4990</v>
+      </c>
+      <c r="H25" t="n">
         <v>105</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>77</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>59</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>593</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="n">
-        <v>384</v>
-      </c>
       <c r="M25" t="n">
+        <v>385</v>
+      </c>
+      <c r="N25" t="n">
         <v>193</v>
       </c>
-      <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
+      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
@@ -3100,7 +3038,9 @@
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
@@ -3124,10 +3064,6 @@
       <c r="AZ25" t="inlineStr"/>
       <c r="BA25" t="inlineStr"/>
       <c r="BB25" t="inlineStr"/>
-      <c r="BC25" t="inlineStr"/>
-      <c r="BD25" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -3155,37 +3091,37 @@
         <v>132</v>
       </c>
       <c r="G26" t="n">
+        <v>14500</v>
+      </c>
+      <c r="H26" t="n">
         <v>103</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>0</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>59</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>593</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="n">
-        <v>384</v>
-      </c>
       <c r="M26" t="n">
+        <v>385</v>
+      </c>
+      <c r="N26" t="n">
         <v>237</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>-1</v>
       </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="n">
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="n">
         <v>-1</v>
       </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -3198,7 +3134,9 @@
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
@@ -3222,10 +3160,6 @@
       <c r="AZ26" t="inlineStr"/>
       <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr"/>
-      <c r="BC26" t="inlineStr"/>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -3250,36 +3184,34 @@
         <v>93</v>
       </c>
       <c r="F27" t="n">
-        <v>133</v>
-      </c>
-      <c r="G27" t="n">
+        <v>134</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
         <v>144</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>14</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>59</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>593</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="n">
-        <v>384</v>
-      </c>
       <c r="M27" t="n">
+        <v>385</v>
+      </c>
+      <c r="N27" t="n">
         <v>237</v>
       </c>
-      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
@@ -3292,7 +3224,9 @@
       <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
       <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
@@ -3316,10 +3250,6 @@
       <c r="AZ27" t="inlineStr"/>
       <c r="BA27" t="inlineStr"/>
       <c r="BB27" t="inlineStr"/>
-      <c r="BC27" t="inlineStr"/>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -3347,37 +3277,37 @@
         <v>132</v>
       </c>
       <c r="G28" t="n">
+        <v>16485</v>
+      </c>
+      <c r="H28" t="n">
         <v>247</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>9</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>59</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>593</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="n">
-        <v>384</v>
-      </c>
       <c r="M28" t="n">
+        <v>385</v>
+      </c>
+      <c r="N28" t="n">
         <v>95</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>-3</v>
       </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="n">
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="n">
         <v>-2</v>
       </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
@@ -3390,7 +3320,9 @@
       <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
@@ -3414,10 +3346,6 @@
       <c r="AZ28" t="inlineStr"/>
       <c r="BA28" t="inlineStr"/>
       <c r="BB28" t="inlineStr"/>
-      <c r="BC28" t="inlineStr"/>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -3445,37 +3373,37 @@
         <v>133</v>
       </c>
       <c r="G29" t="n">
+        <v>19500</v>
+      </c>
+      <c r="H29" t="n">
         <v>235</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>69</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>59</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>593</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="n">
-        <v>384</v>
-      </c>
       <c r="M29" t="n">
+        <v>385</v>
+      </c>
+      <c r="N29" t="n">
         <v>58</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>-2</v>
       </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="n">
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="n">
         <v>-1</v>
       </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
@@ -3488,7 +3416,9 @@
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
       <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
@@ -3512,10 +3442,6 @@
       <c r="AZ29" t="inlineStr"/>
       <c r="BA29" t="inlineStr"/>
       <c r="BB29" t="inlineStr"/>
-      <c r="BC29" t="inlineStr"/>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -3543,33 +3469,33 @@
         <v>132</v>
       </c>
       <c r="G30" t="n">
+        <v>15057</v>
+      </c>
+      <c r="H30" t="n">
         <v>153</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>24</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>59</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>593</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="n">
-        <v>384</v>
-      </c>
       <c r="M30" t="n">
+        <v>385</v>
+      </c>
+      <c r="N30" t="n">
         <v>114</v>
       </c>
-      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
+      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
@@ -3582,7 +3508,9 @@
       <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
@@ -3606,10 +3534,6 @@
       <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="inlineStr"/>
       <c r="BB30" t="inlineStr"/>
-      <c r="BC30" t="inlineStr"/>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -3637,101 +3561,99 @@
         <v>132</v>
       </c>
       <c r="G31" t="n">
+        <v>12566</v>
+      </c>
+      <c r="H31" t="n">
         <v>102</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>22</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>59</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>593</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>160</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>243</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>-4</v>
       </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="n">
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="n">
         <v>-2</v>
       </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
-      <c r="Y31" t="inlineStr"/>
-      <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>2.795454545454533</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.5025252525252561</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-7.199494949494948</v>
+      </c>
+      <c r="V31" t="n">
+        <v>-5617424.242424244</v>
+      </c>
+      <c r="W31" t="n">
+        <v>-0.5175264550264551</v>
+      </c>
+      <c r="X31" t="n">
+        <v>-8.967171717171723</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>-2.010141093474402</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-0.5681818181818177</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-7.385030864197532</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>-3627911.430776014</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>-7.633377425044088</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>-2.067405202821874</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1</v>
+      </c>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="n">
-        <v>-7.315454545454543</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>-5551460.227272727</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>-8.568181818181827</v>
-      </c>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="n">
-        <v>-0.7650000431331989</v>
-      </c>
+      <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="n">
-        <v>-0.5927272727272723</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0.09363636363636729</v>
-      </c>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
       <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="n">
-        <v>-1.476321299171843</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>2.212499999999977</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>-0.4965362318840578</v>
-      </c>
+      <c r="AV31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr"/>
+      <c r="AX31" t="inlineStr"/>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr"/>
-      <c r="BA31" t="n">
-        <v>-7.385863828502423</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>-7.660454710144919</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>-3540577.341054174</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>1</v>
-      </c>
+      <c r="BA31" t="inlineStr"/>
+      <c r="BB31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -3759,37 +3681,37 @@
         <v>132</v>
       </c>
       <c r="G32" t="n">
+        <v>13090</v>
+      </c>
+      <c r="H32" t="n">
         <v>204</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>60</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>59</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>593</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="n">
-        <v>384</v>
-      </c>
       <c r="M32" t="n">
+        <v>385</v>
+      </c>
+      <c r="N32" t="n">
         <v>58</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>-1</v>
       </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="n">
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="n">
         <v>-1</v>
       </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
+      <c r="R32" t="inlineStr"/>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
@@ -3802,7 +3724,9 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
       <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
@@ -3826,10 +3750,6 @@
       <c r="AZ32" t="inlineStr"/>
       <c r="BA32" t="inlineStr"/>
       <c r="BB32" t="inlineStr"/>
-      <c r="BC32" t="inlineStr"/>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
